--- a/data-source/ESTOQUEQUIMICOSPARAGUAI.xlsx
+++ b/data-source/ESTOQUEQUIMICOSPARAGUAI.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="14" documentId="8_{0895E4E1-762B-46C0-BB49-9932679A989C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44744C6A-3EC7-4FF0-83F5-823C87C9618A}"/>

--- a/data-source/ESTOQUEQUIMICOSPARAGUAI.xlsx
+++ b/data-source/ESTOQUEQUIMICOSPARAGUAI.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="14" documentId="8_{0895E4E1-762B-46C0-BB49-9932679A989C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44744C6A-3EC7-4FF0-83F5-823C87C9618A}"/>

--- a/data-source/ESTOQUEQUIMICOSPARAGUAI.xlsx
+++ b/data-source/ESTOQUEQUIMICOSPARAGUAI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\QUIMICOS-ANALISE\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{0895E4E1-762B-46C0-BB49-9932679A989C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44744C6A-3EC7-4FF0-83F5-823C87C9618A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D5A283-3BA7-49DD-956B-4E77633241D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ECA29F79-BACD-416B-AA3B-062F872EA4B8}"/>
   </bookViews>
@@ -633,7 +633,7 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -718,7 +718,7 @@
         <v>14</v>
       </c>
       <c r="C12">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="D12">
         <v>9</v>
@@ -803,7 +803,7 @@
         <v>18</v>
       </c>
       <c r="C17">
-        <v>11700</v>
+        <v>9540</v>
       </c>
       <c r="D17">
         <v>9</v>
@@ -820,7 +820,7 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>9720</v>
+        <v>9000</v>
       </c>
       <c r="D18">
         <v>9</v>
@@ -837,7 +837,7 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>10620</v>
+        <v>9630</v>
       </c>
       <c r="D19">
         <v>9</v>
@@ -854,7 +854,7 @@
         <v>17</v>
       </c>
       <c r="C20">
-        <v>10980</v>
+        <v>10260</v>
       </c>
       <c r="D20">
         <v>9</v>
@@ -871,7 +871,7 @@
         <v>19</v>
       </c>
       <c r="C21">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="D21">
         <v>9</v>
@@ -905,7 +905,7 @@
         <v>20</v>
       </c>
       <c r="C23">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="D23">
         <v>9</v>

--- a/data-source/ESTOQUEQUIMICOSPARAGUAI.xlsx
+++ b/data-source/ESTOQUEQUIMICOSPARAGUAI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\OneDrive\Área de Trabalho\QUIMICOS-ANALISE\data-source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D5A283-3BA7-49DD-956B-4E77633241D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0786F2C-F0A3-4512-B06D-A960B0794F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ECA29F79-BACD-416B-AA3B-062F872EA4B8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="23">
   <si>
     <t>Produto</t>
   </si>
@@ -132,7 +132,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,6 +142,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -172,12 +178,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -514,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{325658FE-4F21-41BB-84C1-3CE3569F3187}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
@@ -541,376 +548,359 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2" s="4">
         <v>4479</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
         <v>250</v>
       </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" s="3">
+        <v>9</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="A3" s="4">
         <v>6505</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="3">
         <v>700</v>
       </c>
-      <c r="D3">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3" s="3">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="4">
         <v>5796</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>150</v>
       </c>
-      <c r="D4">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" s="3">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="A5" s="4">
         <v>6509</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>150</v>
       </c>
-      <c r="D5">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D5" s="3">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="A6" s="4">
         <v>6513</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
+      <c r="B6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3">
         <v>50</v>
       </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D6" s="3">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="A7" s="4">
         <v>6511</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="3">
         <v>350</v>
       </c>
-      <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" s="3">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="A8" s="4">
         <v>6508</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
         <v>600</v>
       </c>
-      <c r="D8">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D8" s="3">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="A9" s="4">
         <v>6510</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="3">
         <v>300</v>
       </c>
-      <c r="D9">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="D9" s="3">
+        <v>9</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="A10" s="4">
         <v>6512</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="3">
         <v>25</v>
       </c>
-      <c r="D10">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D10" s="3">
+        <v>9</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>6511</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11">
-        <v>150</v>
-      </c>
-      <c r="D11">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="A11" s="4">
+        <v>4478</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1700</v>
+      </c>
+      <c r="D11" s="3">
+        <v>9</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+      <c r="A12" s="4">
+        <v>16684</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1260</v>
+      </c>
+      <c r="D12" s="3">
+        <v>9</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>11378</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="3">
+        <v>720</v>
+      </c>
+      <c r="D13" s="3">
+        <v>9</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>11370</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3420</v>
+      </c>
+      <c r="D14" s="3">
+        <v>9</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>16684</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1980</v>
+      </c>
+      <c r="D15" s="3">
+        <v>9</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>16336</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="3">
+        <v>9540</v>
+      </c>
+      <c r="D16" s="3">
+        <v>9</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>11370</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="3">
+        <v>9000</v>
+      </c>
+      <c r="D17" s="3">
+        <v>9</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>16336</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="3">
+        <v>9360</v>
+      </c>
+      <c r="D18" s="3">
+        <v>9</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>11370</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3">
+        <v>10260</v>
+      </c>
+      <c r="D19" s="3">
+        <v>9</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
+        <v>5797</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="3">
+        <v>350</v>
+      </c>
+      <c r="D20" s="3">
+        <v>9</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
         <v>4478</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C12">
-        <v>1700</v>
-      </c>
-      <c r="D12">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>16684</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13">
-        <v>1260</v>
-      </c>
-      <c r="D13">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>11378</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14">
-        <v>720</v>
-      </c>
-      <c r="D14">
-        <v>9</v>
-      </c>
-      <c r="E14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>11370</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15">
-        <v>3420</v>
-      </c>
-      <c r="D15">
-        <v>9</v>
-      </c>
-      <c r="E15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>16684</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16">
-        <v>1980</v>
-      </c>
-      <c r="D16">
-        <v>9</v>
-      </c>
-      <c r="E16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>16336</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17">
-        <v>9540</v>
-      </c>
-      <c r="D17">
-        <v>9</v>
-      </c>
-      <c r="E17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>11370</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18">
-        <v>9000</v>
-      </c>
-      <c r="D18">
-        <v>9</v>
-      </c>
-      <c r="E18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>16336</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19">
-        <v>9630</v>
-      </c>
-      <c r="D19">
-        <v>9</v>
-      </c>
-      <c r="E19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>11370</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20">
-        <v>10260</v>
-      </c>
-      <c r="D20">
-        <v>9</v>
-      </c>
-      <c r="E20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
-        <v>5797</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21">
+      <c r="C21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="D21" s="3">
+        <v>9</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
+        <v>6506</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="3">
         <v>350</v>
       </c>
-      <c r="D21">
-        <v>9</v>
-      </c>
-      <c r="E21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <v>4478</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22">
-        <v>1000</v>
-      </c>
-      <c r="D22">
-        <v>9</v>
-      </c>
-      <c r="E22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
-        <v>6506</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23">
-        <v>350</v>
-      </c>
-      <c r="D23">
-        <v>9</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="D22" s="3">
+        <v>9</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>21</v>
       </c>
     </row>

--- a/data-source/ESTOQUEQUIMICOSPARAGUAI.xlsx
+++ b/data-source/ESTOQUEQUIMICOSPARAGUAI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0786F2C-F0A3-4512-B06D-A960B0794F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{50D5A283-3BA7-49DD-956B-4E77633241D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98D64399-6E87-4AB0-B54D-6E40204ECDFC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ECA29F79-BACD-416B-AA3B-062F872EA4B8}"/>
   </bookViews>
@@ -132,7 +132,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,12 +142,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC0C0C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,13 +172,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -548,359 +541,359 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+      <c r="A2" s="2">
         <v>4479</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2">
         <v>250</v>
       </c>
-      <c r="D2" s="3">
-        <v>9</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="A3" s="2">
         <v>6505</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3">
         <v>700</v>
       </c>
-      <c r="D3" s="3">
-        <v>9</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="D3">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+      <c r="A4" s="2">
         <v>5796</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4">
         <v>150</v>
       </c>
-      <c r="D4" s="3">
-        <v>9</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="D4">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="A5" s="2">
         <v>6509</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5">
         <v>150</v>
       </c>
-      <c r="D5" s="3">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="D5">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+      <c r="A6" s="2">
         <v>6513</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
         <v>50</v>
       </c>
-      <c r="D6" s="3">
-        <v>9</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+      <c r="A7" s="2">
         <v>6511</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7">
         <v>350</v>
       </c>
-      <c r="D7" s="3">
-        <v>9</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="D7">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+      <c r="A8" s="2">
         <v>6508</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8">
         <v>600</v>
       </c>
-      <c r="D8" s="3">
-        <v>9</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="D8">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
+      <c r="A9" s="2">
         <v>6510</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9">
         <v>300</v>
       </c>
-      <c r="D9" s="3">
-        <v>9</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="D9">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
+      <c r="A10" s="2">
         <v>6512</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10">
         <v>25</v>
       </c>
-      <c r="D10" s="3">
-        <v>9</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
+      <c r="A11" s="2">
         <v>4478</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="3">
-        <v>1700</v>
-      </c>
-      <c r="D11" s="3">
-        <v>9</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="C11">
+        <v>1650</v>
+      </c>
+      <c r="D11">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
+      <c r="A12" s="2">
         <v>16684</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12">
         <v>1260</v>
       </c>
-      <c r="D12" s="3">
-        <v>9</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="D12">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
+      <c r="A13" s="2">
         <v>11378</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13">
         <v>720</v>
       </c>
-      <c r="D13" s="3">
-        <v>9</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="D13">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+      <c r="A14" s="2">
         <v>11370</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="3">
-        <v>3420</v>
-      </c>
-      <c r="D14" s="3">
-        <v>9</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="C14">
+        <v>3240</v>
+      </c>
+      <c r="D14">
+        <v>9</v>
+      </c>
+      <c r="E14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
+      <c r="A15" s="2">
         <v>16684</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15">
         <v>1980</v>
       </c>
-      <c r="D15" s="3">
-        <v>9</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="D15">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
+      <c r="A16" s="2">
         <v>16336</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16">
         <v>9540</v>
       </c>
-      <c r="D16" s="3">
-        <v>9</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="D16">
+        <v>9</v>
+      </c>
+      <c r="E16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
+      <c r="A17" s="2">
         <v>11370</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17">
         <v>9000</v>
       </c>
-      <c r="D17" s="3">
-        <v>9</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="D17">
+        <v>9</v>
+      </c>
+      <c r="E17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
+      <c r="A18" s="2">
         <v>16336</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18">
         <v>9360</v>
       </c>
-      <c r="D18" s="3">
-        <v>9</v>
-      </c>
-      <c r="E18" s="3" t="s">
+      <c r="D18">
+        <v>9</v>
+      </c>
+      <c r="E18" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
+      <c r="A19" s="2">
         <v>11370</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19">
         <v>10260</v>
       </c>
-      <c r="D19" s="3">
-        <v>9</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="D19">
+        <v>9</v>
+      </c>
+      <c r="E19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="4">
+      <c r="A20" s="2">
         <v>5797</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20">
         <v>350</v>
       </c>
-      <c r="D20" s="3">
-        <v>9</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="D20">
+        <v>9</v>
+      </c>
+      <c r="E20" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
+      <c r="A21" s="2">
         <v>4478</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21">
         <v>1000</v>
       </c>
-      <c r="D21" s="3">
-        <v>9</v>
-      </c>
-      <c r="E21" s="3" t="s">
+      <c r="D21">
+        <v>9</v>
+      </c>
+      <c r="E21" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
+      <c r="A22" s="2">
         <v>6506</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22">
         <v>350</v>
       </c>
-      <c r="D22" s="3">
-        <v>9</v>
-      </c>
-      <c r="E22" s="3" t="s">
+      <c r="D22">
+        <v>9</v>
+      </c>
+      <c r="E22" t="s">
         <v>21</v>
       </c>
     </row>

--- a/data-source/ESTOQUEQUIMICOSPARAGUAI.xlsx
+++ b/data-source/ESTOQUEQUIMICOSPARAGUAI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{50D5A283-3BA7-49DD-956B-4E77633241D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98D64399-6E87-4AB0-B54D-6E40204ECDFC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E7F228-F4C8-46F5-94C8-FF77FB7ED66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ECA29F79-BACD-416B-AA3B-062F872EA4B8}"/>
   </bookViews>
@@ -132,7 +132,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,6 +142,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -172,12 +178,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -547,13 +554,13 @@
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
-        <v>250</v>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C2" s="4">
+        <v>200</v>
+      </c>
+      <c r="D2" s="4">
+        <v>9</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -564,13 +571,13 @@
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="4">
         <v>700</v>
       </c>
-      <c r="D3">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3" s="4">
+        <v>9</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -581,13 +588,13 @@
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <v>150</v>
       </c>
-      <c r="D4">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" s="4">
+        <v>9</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -598,13 +605,13 @@
       <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="4">
         <v>150</v>
       </c>
-      <c r="D5">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D5" s="4">
+        <v>9</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -612,16 +619,16 @@
       <c r="A6" s="2">
         <v>6513</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
+      <c r="B6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4">
         <v>50</v>
       </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D6" s="4">
+        <v>9</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -632,13 +639,13 @@
       <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="4">
         <v>350</v>
       </c>
-      <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" s="4">
+        <v>9</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -649,13 +656,13 @@
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="4">
         <v>600</v>
       </c>
-      <c r="D8">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D8" s="4">
+        <v>9</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -666,13 +673,13 @@
       <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="4">
         <v>300</v>
       </c>
-      <c r="D9">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="D9" s="4">
+        <v>9</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -683,13 +690,13 @@
       <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="4">
         <v>25</v>
       </c>
-      <c r="D10">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D10" s="4">
+        <v>9</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -700,13 +707,13 @@
       <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C11">
-        <v>1650</v>
-      </c>
-      <c r="D11">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="C11" s="4">
+        <v>1600</v>
+      </c>
+      <c r="D11" s="4">
+        <v>9</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -717,13 +724,13 @@
       <c r="B12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="4">
         <v>1260</v>
       </c>
-      <c r="D12">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="D12" s="4">
+        <v>9</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -734,13 +741,13 @@
       <c r="B13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="4">
         <v>720</v>
       </c>
-      <c r="D13">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="D13" s="4">
+        <v>9</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -751,13 +758,13 @@
       <c r="B14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C14">
-        <v>3240</v>
-      </c>
-      <c r="D14">
-        <v>9</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="C14" s="4">
+        <v>1800</v>
+      </c>
+      <c r="D14" s="4">
+        <v>9</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -768,13 +775,13 @@
       <c r="B15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="4">
         <v>1980</v>
       </c>
-      <c r="D15">
-        <v>9</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="D15" s="4">
+        <v>9</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -785,13 +792,13 @@
       <c r="B16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C16">
-        <v>9540</v>
-      </c>
-      <c r="D16">
-        <v>9</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="C16" s="4">
+        <v>8640</v>
+      </c>
+      <c r="D16" s="4">
+        <v>9</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -802,13 +809,13 @@
       <c r="B17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C17">
-        <v>9000</v>
-      </c>
-      <c r="D17">
-        <v>9</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="C17" s="4">
+        <v>8280</v>
+      </c>
+      <c r="D17" s="4">
+        <v>9</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -819,13 +826,13 @@
       <c r="B18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C18">
-        <v>9360</v>
-      </c>
-      <c r="D18">
-        <v>9</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="C18" s="4">
+        <v>7380</v>
+      </c>
+      <c r="D18" s="4">
+        <v>9</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -836,13 +843,13 @@
       <c r="B19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C19">
-        <v>10260</v>
-      </c>
-      <c r="D19">
-        <v>9</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="C19" s="4">
+        <v>9900</v>
+      </c>
+      <c r="D19" s="4">
+        <v>9</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -853,13 +860,13 @@
       <c r="B20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C20">
-        <v>350</v>
-      </c>
-      <c r="D20">
-        <v>9</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="C20" s="4">
+        <v>200</v>
+      </c>
+      <c r="D20" s="4">
+        <v>9</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -870,13 +877,13 @@
       <c r="B21" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C21">
-        <v>1000</v>
-      </c>
-      <c r="D21">
-        <v>9</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="C21" s="4">
+        <v>950</v>
+      </c>
+      <c r="D21" s="4">
+        <v>9</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -887,13 +894,13 @@
       <c r="B22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C22">
-        <v>350</v>
-      </c>
-      <c r="D22">
-        <v>9</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="C22" s="4">
+        <v>50</v>
+      </c>
+      <c r="D22" s="4">
+        <v>9</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>21</v>
       </c>
     </row>
